--- a/evaluasi chatbot.xlsx
+++ b/evaluasi chatbot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aqil Anhein\Desktop\TA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CCFF26-F76A-4068-9F0A-B261389AE31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713A9DBB-0E2C-4B00-9F40-3DE5217BC1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF7CA626-8266-4772-A1CA-D06501DAC506}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Traditional RAG" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$D$52</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="114">
   <si>
     <t>Pertanyaan</t>
   </si>
@@ -45,16 +48,10 @@
     <t>Jawaban</t>
   </si>
   <si>
-    <t>Jenis Pertanyaan</t>
-  </si>
-  <si>
     <t>Correct?</t>
   </si>
   <si>
     <t>apa isi pasal 5 Peraturan pemerintah no 50 thn 2012</t>
-  </si>
-  <si>
-    <t>Direct</t>
   </si>
   <si>
     <t>Pasal 5 Peraturan Pemerintah No. 50 Tahun 2012 mengatur tentang kewajiban penerapan Sistem Manajemen Keselamatan dan Kesehatan Kerja (SMK3) oleh perusahaan. Berikut adalah isi dari Pasal 5:
@@ -75,9 +72,6 @@
 Perjanjian Kerja Bersama: Pasal 132 UU No. 13 Tahun 2003 menyatakan bahwa perjanjian kerja bersama dapat mengatur ketentuan lebih lanjut mengenai kerja lembur, termasuk besaran upah lembur.
 Pendaftaran Perjanjian: Perjanjian kerja bersama yang mengatur kerja lembur harus didaftarkan oleh pengusaha pada instansi yang bertanggung jawab di bidang ketenagakerjaan.
 Untuk informasi lebih lanjut dan detail mengenai ketentuan kerja lembur, Anda dapat merujuk kepada Pasal 77 dan Pasal 132 UU No. 13 Tahun 2003 serta Peraturan Pemerintah No. 36 Tahun 2021.</t>
-  </si>
-  <si>
-    <t>Semantic</t>
   </si>
   <si>
     <t>apa itu persero</t>
@@ -714,7 +708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -742,19 +736,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -763,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -782,8 +763,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1143,852 +1123,767 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E46E19-AE99-46EA-92B3-7EC24238164E}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="60.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="180.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" ht="180.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="324.75" x14ac:dyDescent="0.25">
+      <c r="E3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="324.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="228.75" x14ac:dyDescent="0.25">
+      <c r="E4" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="228.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="228.75" x14ac:dyDescent="0.25">
+      <c r="E5" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="228.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="204.75" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="372.75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="372.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="204.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="192.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="192.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="24.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="96.75" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="96.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="144.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="144.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="252.75" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="252.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="180.75" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="180.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="C19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="180.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="108.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="132.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="396.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="348.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="132.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="168.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="180.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="180.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="168.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="288.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="240.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="216.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="312.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B47" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="324.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="288.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B50" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="252.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" ht="228.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54">
+        <f>COUNTIF(E2:E52,"TP")</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55">
+        <f>COUNTIF(E2:E52,"TN")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>98</v>
+      </c>
+      <c r="E56">
+        <f>COUNTIF(E2:E52,"FN")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
+      <c r="E59">
+        <f>E54/(E54)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="180.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="E60">
+        <f>E54/(E54+E56)</f>
+        <v>0.88372093023255816</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61">
+        <f>2*(E59*E60)/(E59+E60)</f>
+        <v>0.93827160493827166</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>100</v>
+      </c>
+      <c r="E62">
+        <f>E55/(E55)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="108.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="132.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="396.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="348.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="132.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="168.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="180.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="180.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" ht="168.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" ht="288.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" ht="240.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="216.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" ht="312.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="312.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" ht="288.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="252.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" ht="228.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E54" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54">
-        <f>COUNTIF(F2:F52,"TP")</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E55" t="s">
-        <v>97</v>
-      </c>
-      <c r="F55">
-        <f>COUNTIF(F2:F52,"TN")</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E56" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56">
-        <f>COUNTIF(F2:F52,"FN")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E58" t="s">
-        <v>98</v>
-      </c>
-      <c r="F58" s="10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E59" t="s">
-        <v>99</v>
-      </c>
-      <c r="F59">
-        <f>F54/(F54)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E60" t="s">
-        <v>100</v>
-      </c>
-      <c r="F60">
-        <f>F54/(F54+F56)</f>
-        <v>0.88372093023255816</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E61" t="s">
-        <v>102</v>
-      </c>
-      <c r="F61">
-        <f>2*(F59*F60)/(F59+F60)</f>
-        <v>0.93827160493827166</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E62" t="s">
-        <v>103</v>
-      </c>
-      <c r="F62">
-        <f>F55/(F55)</f>
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="B2:D52" xr:uid="{92E46E19-AE99-46EA-92B3-7EC24238164E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2004,155 +1899,155 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>3</v>
+      <c r="D2" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="42" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="14">
+      <c r="B3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>105</v>
+      <c r="B4" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>108</v>
+      <c r="B5" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>105</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="16">
+      <c r="C8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="16">
-        <v>1</v>
-      </c>
-    </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="15"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="15"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="16"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="15"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="16"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="16"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="16"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="16"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="15"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
-      <c r="C21" s="17"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="18"/>
+      <c r="C22" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
